--- a/docs/manual_test_plan.xlsx
+++ b/docs/manual_test_plan.xlsx
@@ -1482,9 +1482,9 @@
         <is>
           <t>1. Hover the 📌 button in the Wells pane's group bar — note its tooltip; it should be highlighted (Pin ON is the default).
 2. Click well B in the tree.
-3. Click 📌 (Pin OFF); click inside Log View 1 to make it active, then click well C in the tree.
-4. Click 📌 again (Pin ON) and click well A.
-   Expected: Step 2 (Pin ON): BOTH Log Views and any plots switch to well B; status Pin ON — every view and plot follows the selected well was shown when toggling. Step 3 (Pin OFF): status Pin OFF — only the active panel follows; other views keep their wells; only Log View 1 switches to C, Log View 2 stays on B; browsing panes (Tops, Inspector) still track the selection. Step 4: everything follows again (all views on A). Do not confuse 📌 with the per-well ★ star — that is the pinned-favourites run scope, unrelated to following.</t>
+3. Click 📌 (Pin OFF); click inside Log View 1 to make it the working pane, then click well C in the tree.
+4. Click inside Log View 2, click well A in the tree, then click 📌 again (Pin ON) and click well B.
+   Expected: Step 2 (Pin ON): BOTH Log Views and any plots switch to well B; status Pin ON — every view and plot follows the selected well was shown when toggling. Step 3 (Pin OFF): status Pin OFF — only the active panel follows; other views keep their wells; only Log View 1 switches to C, Log View 2 stays on B; browsing panes (Tops, Inspector) still track the selection. Step 4: Log View 2 (the pane you clicked into last) takes C→A while Log View 1 keeps C; then with the pin back ON everything follows to B. "Active panel" means the viewer you last clicked into — clicking a well in the tree does not hand the role to the tree, so with the pin off exactly one viewer always follows. Do not confuse 📌 with the per-well ★ star — that is the pinned-favourites run scope, unrelated to following.</t>
         </is>
       </c>
     </row>
@@ -1522,9 +1522,9 @@
           <t>1. Right-click the Crossplot canvas, then the empty grey background of a pane.
 2. Right-click a ribbon button, a well row in the tree, and a pane toolbar.
 3. Right-click inside a text input (e.g. the session-name field or SQL editor).
-4. Press F5, then Ctrl+R; in the dialog press Escape once, then repeat and click Cancel; finally press the mouse Back (side) button.
+4. Press F5; dismiss the dialog with Escape. Press Ctrl+R; dismiss it by clicking Cancel. Press F5 and then, with the dialog still up, press Ctrl+R again. Finally press the mouse Back (side) button.
 5. Single-click the module pane's number field, then double-click it.
-   Expected: Step 1: the custom app context menu appears (panel-specific items + window actions like Split right / Split down). Step 2: NO menu at all (native WebView menu suppressed — a stray "Refresh" there would wipe the workspace). Step 3: the native EDIT menu appears (undo/cut/copy/paste — no Refresh/Back). Step 4: a blocking confirm "Reload SandiBumi? The workspace re-opens from its last saved state…" with Cancel / red Reload; Escape and Cancel both dismiss without reloading; mouse Back/Forward do nothing. Step 5: first click only arms the field (status tip "Number fields arm on click — double-click to edit", no caret); double-click enters edit with the value selected — a stray click+scroll can never change a parameter.</t>
+   Expected: Step 1: the custom app context menu appears (panel-specific items + window actions like Split right / Split down) — on a plot canvas that menu leads with Properties…, so the plot's own settings and the window actions are both one click away. Step 2: NO menu at all (native WebView menu suppressed — a stray "Refresh" there would wipe the workspace). Step 3: the native EDIT menu appears (undo/cut/copy/paste — no Refresh/Back). Step 4: each of F5 and Ctrl+R raises the same blocking confirm "Reload SandiBumi? The workspace re-opens from its last saved state…" with Cancel / red Reload; Escape and Cancel both dismiss without reloading; a second reload key pressed while the dialog is already up does NOT open a second dialog — it briefly pulses the open one, so the key is visibly acknowledged; mouse Back/Forward do nothing. Step 5: first click only arms the field (status tip "Number fields arm on click — double-click to edit", no caret); double-click enters edit with the value selected — a stray click+scroll can never change a parameter.</t>
         </is>
       </c>
     </row>

--- a/docs/manual_test_plan.xlsx
+++ b/docs/manual_test_plan.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tests'!$A$1:$J$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tests'!$A$1:$J$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:J266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4309,11 +4309,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr"/>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G69" s="8" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Synthetic Log (KNN Predict) pane (`log_predict`, modules.rs; workflow.rs output-masking)</t>
@@ -4331,8 +4327,8 @@
 3. Now the washout-repair case: TARGET = RHOB, OPT_COMBINE = MAX_RAW, Mask = BADHOLE. Run. Inspect RHOB_SYN inside a BADHOLE = 1 washout.
 4. Negative: run with TARGET = a curve with under 10 valid samples (or scope a nearly-empty well).
    Expected: Step 2: filled values are plausible DT (within the well's DT range, tracking lithology — high in shale/coal, low in tight streaks); no extrapolated nonsense outside predictor coverage. Step 4: all-MISSING output reported as ⚠ "no finite output", not green success. Step 3 SHOULD show a finite repaired RHOB inside the washout (that is the module's purpose), but see below.
-   Known issue: AUDIT-2026-07-21 finding "log_predict's MAX_RAW/repaired-synthetic value is unconditionally re-blanked at masked (washout) depths by workflow.rs's output-masking step" (§Prep statistical #1, CONFIRMED; still unfixed — listed in REVIEW.md Round 4 under "6 findings that … await your sign-off"). Expect step 3 to FAIL: RHOB_SYN will be NaN exactly inside the masked washout it exists to fill. Log as known.
-   Automated coverage - pinned (pile B, 2026-07-31): `a_synthetic_log_fills_gaps_keeps_raw_and_repairs_only_downward` (modules.rs) plus `a_masked_washout_defeats_the_very_module_meant_to_repair_it` (workflow.rs). The second one pins the audited defect AS-IS, not as correct behaviour.</t>
+   Fixed (SB-ENV-027 / DEC-033, 2026-08-18): the AUDIT-2026-07-21 finding (repaired value re-blanked at masked depths) is closed. The ONE declared repair - `log_predict.SYN` under OPT_COMBINE = MAX_RAW - is exempt from BOTH mask passes, so step 3 now shows a finite repaired RHOB inside the washout, plus a companion `RHOB_SYN_RECON_FLAG` = 1 exactly there ("reconstructed, not measured"). SYNTHETIC and FILL_MISSING stay masked normally - the exemption is per output AND per mode.
+   Automated coverage - pinned: `a_synthetic_log_fills_gaps_keeps_raw_and_repairs_only_downward` (modules.rs), `the_masked_washout_is_now_repaired_by_the_declared_exemption_it_once_defeated` (workflow.rs, the inverted former defect pin) and `the_one_declared_repair_survives_the_mask_and_wears_its_marker_while_other_modes_stay_masked` (workflow.rs).</t>
         </is>
       </c>
     </row>
@@ -4558,10 +4554,11 @@
           <t>1. In the same pane change `OPT_GR` to LARINOV1 (Larionov, Mesozoic and older — corrected
    2026-07-31, see the note under the Expected line); Run.
 2. Repeat for LARINOV2, STIEBER1, CLAVIER (four more runs, same Output cons `INTERP`).
+2b. DEC-096. Repeat once more with LARINOV2_NORM. Read `VSH_GR` at the shale end: it closes on exactly 1.000 where `LARINOV2` stops at 0.9957, and it reads 0.43 % higher than `LARINOV2` at every IGR, not only at the endpoint. Same for LARINOV1_NORM against `LARINOV1` at 1.00 %.
 3. Open Curve Catalog and inspect the versioned-run list under Constellations; hover a version row.
    Expected: Each re-run lands as version N+1 (never overwrites; catalog list shows "vsh_gr · \&lt;timestamp&gt;" per run, hover tooltip lists params so you can tell which OPT_GR each version used). Domain: at intermediate GR every nonlinear VSH &lt; the LINEAR VSH (all corrections concave — e.g. linear 0.50 → Larionov-older (`LARINOV1`) ≈0.33, Larionov-Tertiary (`LARINOV2`) ≈0.22); endpoints 0 and 1 unchanged; all limited VSH stay 0–1.
    THE LARIONOV LABELS WERE REVERSED HERE — CORRECTED IN THE TEXT ABOVE 2026-07-31, finding 21. Step 1 used to call `LARINOV1` "Larionov Tertiary" and the Expected line paired Tertiary with ≈0.33 and older-rocks with ≈0.22. Both were backwards relative to what the code computes. The dropdown now states the rock age itself (2026-08-01) — `LARINOV1 — Larionov, Mesozoic and older`, `LARINOV2 — Larionov, Tertiary / unconsolidated` — so the plan is no longer the only place this is written down, and `the_vsh_gr_labels_agree_with_the_coefficients_they_describe` keeps the two from drifting apart again. The option ids are unchanged, because they are stored in `params_json` on every saved run. `LARINOV1` is `0.33*(2^(2*IGR) - 1)` — Larionov for older rocks, Mesozoic and older, giving 0.330 at IGR 0.5. `LARINOV2` is `0.083*(2^(3.7*IGR) - 1)` — Larionov for Tertiary / unconsolidated, giving 0.216. The code matches the published coefficient sets; the labels in this step do not. Mahakam Delta is Miocene, so the transform you almost certainly want is LARINOV2, and picking LARINOV1 on the label above would overstate shale volume by more than half through the whole intermediate-GR interval — where the VSH cutoff decides net pay, with nothing on the log to show for it.
-   A second correction to the Expected line: "endpoints 0 and 1 unchanged" does not hold for the Larionov forms, and that is not a defect. They are empirical fits that were never normalized to close at pure shale: at IGR 1, LARINOV1 stops at 0.99, LARINOV2 at 0.9957, and LARINOV3 overshoots to 1.133. LINEAR, all three Stieber forms and Clavier do land on exactly 1.0 (Clavier cancels exactly, 1.7 − sqrt(0.49) = 1.0). VSH clamps every one of them into 0–1; VSH_GR keeps the raw value. That difference is what the two outputs are for, so read VSH for the answer and VSH_GR when you want to see the transform's own behaviour.
+   A second correction to the Expected line: "endpoints 0 and 1 unchanged" does not hold for the PUBLISHED Larionov forms — and since 2026-08-22 there is a normalised pair that does close (DEC-096, SB-CLY-004). `LARINOV1_NORM` and `LARINOV2_NORM` are `(2^(k·IGR)−1)/(2^k−1)` and land on exactly 1.0; `LARINOV1`/`LARINOV2` keep the vendors' published decimals for digit-for-digit parity and are labelled as such. `LARINOV3` is deliberately NOT normalised: nothing in the repo cites a source for that form, so there is no published pair to normalise against, and inventing one is the move the provenance rules forbid. The published forms are empirical fits that were never normalized to close at pure shale: at IGR 1, LARINOV1 stops at 0.99, LARINOV2 at 0.9957, and LARINOV3 overshoots to 1.133. LINEAR, all three Stieber forms and Clavier do land on exactly 1.0 (Clavier cancels exactly, 1.7 − sqrt(0.49) = 1.0). VSH clamps every one of them into 0–1; VSH_GR keeps the raw value. That difference is what the two outputs are for, so read VSH for the answer and VSH_GR when you want to see the transform's own behaviour.
    Automated coverage - pinned (pile B, 2026-07-31): `every_vsh_gr_transform_lands_on_its_published_coefficient` (modules.rs) evaluates ALL EIGHT options at IGR 0.5 against their published closed forms computed by hand — so it is a check, not a snapshot of a run — plus both endpoints, the clamping, the concavity claim (every nonlinear form reads below LINEAR at intermediate GR), and monotonicity in GR, which is where a sign or bracket slip hides when the endpoints still look right. `re_running_a_module_bumps_the_set_version_and_keeps_every_earlier_run` (equations.rs) covers step 3: five runs give five versions each carrying its own OPT_GR in the params record, a different set name versions independently, and a well that has never been run starts at 1 whatever its neighbours are on.</t>
         </is>
       </c>
@@ -5720,7 +5717,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>1. Advance ▸ IMTS, scope Selection. Defaults: RT = RES_DEEP, PHIT = PHIT_SSC, VKAOL = VDCL, SWIRR = SWIRR_T, CBW = CBW; set RW and TEMP_C to your zone values; MSTAR/NSTAR 1.9, S_FACTOR 0.5, CEC_KAOL 8 / CEC_ILL 25. Run.
+          <t>1. Advance ▸ IMTS, scope Selection. Defaults: RT = RES_DEEP, PHIT = PHIT_SSC, VKAOL = VDCL, SWIRR = SWIRR_T, CBW = CBW; set RW and TEMP_C to your zone values; MSTAR/NSTAR 1.9, CEC_KAOL 8 / CEC_ILL 25, RHO_KAOL 2.62 / RHO_ILL 2.78. S_FACTOR_GW ships absent and the run REFUSES without it (DEC-094) - fit it first with Advance ▸ Calibrate S…, whose PHIT curve is required because the plug's own porosity is part of the grain-weight basis. Run.
 2. Log View: SWT_IMTS/SWE_IMTS next to SWE_INDO and SWT_RTC; add QVEFF.
    Expected: SWT_IMTS ∈ [0,1]; QVEFF ≥ 0, rising with clay volume and shrinking porosity; in high-clay LRLC pay SWT_IMTS reads LOWER than SWE_INDO and broadly agrees with SWT_RTC (the two excess-conductivity methods should tell the same geological story); clean water sand ~1 for all. Curve Catalog + History entries as usual.</t>
         </is>
@@ -5958,10 +5955,19 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>1. Advance ▸ SandiMin…. Verify: components box grouped Minerals / Clays / Fluids (fluids badged flushed/unflushed) with Quartz, Illite, Water Sxo, Water Sw pre-ticked; tool rows with curve + σ fields (Formation Density 0.0264, Neutron 0.014, Sonic Transit Time 1.951, Total Gamma Ray 6, Unflushed Conductivity (from RT) → RES_DEEP with σ blank = "auto"); Fluid properties (CT/CXO — resistivity → conductivity) box with Rw/Rmf/temps/m/n/Mud and a live preview line (w=… Cw=… Cbw=…).
+          <t>1. Advance ▸ SandiMin…. Verify: components box grouped Minerals / Clays / Fluids (fluids badged flushed/unflushed) with Quartz, Illite, Water Sxo, Water Sw pre-ticked; tool rows with curve + σ fields (Formation Density 0.0264, Neutron 0.014, Sonic Transit Time 1.951, Total Gamma Ray 6, Unflushed Conductivity (from RT) → RES_DEEP with σ blank = "auto"); Fluid properties (CT/CXO — resistivity → conductivity) box with Rw/Rmf/temps/m/n/Mud, the three DEC-095 fields Water salinity (ppm) / Filtrate salinity (ppm) (both blank, placeholders reading "from Rw" / "from Rmf") and α ceiling (5), and a live preview line (w=… Cw=… Cbw=… α(x/u)=… salinity(w/mf)=… ppm).
 2. In the Autofill from precalc row leave "(whole well)" and click Read → Formation temp (°F) and Rmf sample fill; status reads "SandiMin autofill (WELL, whole well): FTEMP … °F, RMF … ohmm (n/n samples)". Repeat with a zone picked (covers REVIEW.md §"SandiMin: wet→dry clay converter + fluid autofill from precalc (#22)" autofill items).
 3. Switch to the second well in the Wells pane: the autofill zone list refreshes to that well's zones (covers §#22 "Switch wells…"). Click Read, then IMMEDIATELY switch back to well 1 before it resolves.
 4. On a well never precalc'd, click Read.
+5. DEC-095, the salinity and the α ceiling. Leave both salinity boxes blank and read the
+   preview's `salinity(w/mf)` — those are the Bateman-Konen back-calculations from Rw and Rmf.
+   Now type 500 into Water salinity (ppm): the preview's salinity jumps to 500 and
+   α(x/u)'s second number pins at 5.00 with (held from …/6.40) appended — the ceiling
+   bound, and the preview says what α would have been. Raise α ceiling to 10: the held-from
+   note disappears and α reads 6.40, which is the reference spec's own uncapped value. Put the
+   ceiling back to 5, run the solver, and confirm the result panel carries an amber line naming
+   ALPHA_MAX and the unheld value. Clear the salinity box again and confirm the preview returns to
+   the derived number — blank must mean *derive it*, never zero.
    Expected: steps 1–2 as described. Step 3: the form is NOT stamped with the wrong well's FTEMP/RMF after the switch (stale response discarded). Step 4: status "SandiMin autofill: no FTEMP_F/RMF samples on … — run the precalc module first"; nothing applied.
    Known issue: AUDIT-2026-07-21 "SandiMin's 'Autofill from precalc' Read button has no stale-response race guard, unlike refreshZones() in the same file" — fixed in the uncommitted Round-4 batch (REVIEW.md §Round 4 "Race guards", unchecked). Expect PASS on step 3; stale values appearing is that finding — log as known.</t>
         </is>
@@ -6542,7 +6548,7 @@
    class 1 (best) and the tighter half is DEMOTED to class 3 (non-net), in the same run, with no
    warning. Worth noting in your Notes as a cross-field validation ticket, since RT_LOG feeds the
    facies tie-in in T-RT-15.
-   Automated coverage - pinned (pile B, 2026-07-31): `an_inverted_cutoff_ladder_is_accepted_and_scatters_the_middle_class` (rocktyping.rs) - the sane 1/2/3 ladder and MISSING propagation, then the inverted case pinned AS-IS.</t>
+   Automated coverage - pinned (pile B, 2026-07-31; ENFORCED 2026-08-20): `a_cutoff_ladder_must_be_monotone_and_an_inverted_one_is_refused_before_it_scatters_a_class` (rocktyping.rs) - the sane 1/2/3 ladder and MISSING propagation unchanged, and the inverted case now REFUSED at `run_module` on both axes rather than pinned AS-IS, with equality allowed because a shared cutoff split on the other axis is a real ladder.</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7921,7 @@
    external-input list is built from log inputs, and MASK is an option. The mask setting is carried
    all the way into the plan and then read by nobody. Still expect MC Net/HPV above the pay-summary
    value.
-   Automated coverage - pinned (pile B, 2026-07-31): `the_monte_carlo_chain_ignores_a_step_mask_the_real_chain_honours` (montecarlo.rs) - it runs the real chain and the Monte Carlo chain over the same masked well and compares them, and asserts BOTH causes. Pins the defect AS-IS.</t>
+   Automated coverage - pinned (pile B, 2026-07-31): `a_monte_carlo_chain_honours_a_step_mask_exactly_as_the_real_chain_does` (montecarlo.rs) - it runs the real chain and the Monte Carlo chain over the same masked well and compares them, and asserts BOTH causes. Pins the defect AS-IS.</t>
         </is>
       </c>
     </row>
@@ -12882,8 +12888,10 @@
           <t>1. Open your current project; check its folder in Explorer.
 2. (Optional) Open the old copy; watch its folder and the console.
    Expected: step 1: NO new `*-backup.duckdb` appears, launch is not slower — absence is
-   the pass. Step 2: a `&lt;name&gt;.pre-1-backup.duckdb` appears BEFORE the rebuild and the launch
-   log announces it; the backup opens as a valid project if pointed at directly.
+   the pass. Step 2: an unstamped legacy source produces
+   `&lt;name&gt;.pre-0-backup.duckdb` BEFORE the rebuild (a stamped source uses its own version),
+   and the launch log announces that exact path; the backup opens as a valid project if
+   pointed at directly.
    Automated coverage - pinned (pile A): a test on the green gate already checks the arithmetic behind this one. What your tick still adds is that the running app surfaces it correctly.</t>
         </is>
       </c>
@@ -12993,9 +13001,670 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-01</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="inlineStr">
+        <is>
+          <t>Build the release candidate from a clean clone, and keep the receipt</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr"/>
+      <c r="F252" s="10" t="inlineStr"/>
+      <c r="G252" s="8" t="inlineStr"/>
+      <c r="H252" s="7" t="inlineStr">
+        <is>
+          <t>`git clone`, `tools\check.ps1`, `npm run tauri build` (CLAUDE.md §Dev commands)</t>
+        </is>
+      </c>
+      <c r="I252" s="7" t="inlineStr">
+        <is>
+          <t>reference machine; the accepted commit hash written down; an empty folder outside every existing checkout (e.g. `C:\sb-clean`); no other cargo build running.</t>
+        </is>
+      </c>
+      <c r="J252" s="7" t="inlineStr">
+        <is>
+          <t>1. Clone the repository into the empty folder and check out the accepted commit; run `npm install` there.
+2. From a vcvars-pinned shell in that clone, run the green gate: `powershell -ExecutionPolicy Bypass -File tools\check.ps1`. Keep the whole log.
+3. In the same shell run `npm run tauri build`.
+4. Record in Notes: the path of the `.msi` under `src-tauri\target\release\bundle\msi\`, its SHA-256 (`certutil -hashfile &lt;msi&gt; SHA256`), the `package.json` version, the identifier `com.sandibumi.petro`, and the commit hash.
+   Expected: The gate log ends GATE GREEN in …s from the clean clone — that is SB-CORE-T13, and until now it has only ever been run in an existing worktree. The build produces exactly one `.msi`; launching the built `sandibumi.exe` shows the launch card with the same version as `package.json`. Known gap: the MSI is unsigned today — signing is SB-INS-001's remaining half. Write "unsigned" in Notes; it is not a Fail of this test.
+   Automation note: `a_signed_clean_machine_msi_must_match_the_installed_identity_and_version` (installation.rs) checks evidence handed to it and has never seen a real MSI; the four values you record here are what it will be fed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-02</t>
+        </is>
+      </c>
+      <c r="C253" s="7" t="inlineStr">
+        <is>
+          <t>Clean-machine install by IT, launch as a standard user (standard_user, locked_down_user)</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E253" s="9" t="inlineStr"/>
+      <c r="F253" s="10" t="inlineStr"/>
+      <c r="G253" s="8" t="inlineStr"/>
+      <c r="H253" s="7" t="inlineStr">
+        <is>
+          <t>`msiexec`, Windows Settings ▸ Apps ▸ Installed apps, the launch card</t>
+        </is>
+      </c>
+      <c r="I253" s="7" t="inlineStr">
+        <is>
+          <t>the clean machine; the MSI from T-INS-01 on media; an admin account, a standard-user account, and a locked-down account (no admin, no write access to Program Files).</t>
+        </is>
+      </c>
+      <c r="J253" s="7" t="inlineStr">
+        <is>
+          <t>1. As the administrator install silently: `msiexec /i &lt;msi&gt; /qn /l*v C:\sb-install.log`. Per machine is the decided scope, and it comes from Tauri's own WiX template (`InstallScope="perMachine"`, embedded in the `@tauri-apps/cli` binary that builds the MSI), not from anything on this command line or in `tauri.conf.json`; confirm it from the log's property dump (`ALLUSERS = 1`) and record the install directory the log names (`INSTALLDIR`) — nothing in the tree fixes that path.
+2. Sign in as the standard user; launch SandiBumi from the Start menu.
+3. Settings ▸ Apps ▸ Installed apps: read SandiBumi's version.
+4. Read the version on the launch card (or the first line of Project ▸ Monitor ▸ Diagnostics… after Build report — there is no About item).
+5. Project ▸ New Project… into the user's Documents; Data ▸ Import Logs ▾ ▸ Import LAS… `SANDI-01.las` from the media; Plot ▸ New Log View.
+6. Sign out; sign in as the locked-down user and repeat steps 2 and 5.
+   Expected: The install log ends with return value 0 and no dialog appeared. The app launches under the standard account without an elevation prompt, and without any network — the WebView2 offline install mode means launch never fetches a runtime. The version in Apps equals the launch-card version equals `package.json`. The project opens, the LAS imports and the log view draws; nothing new appears under the install directory afterwards. The locked-down user gets the same result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-03</t>
+        </is>
+      </c>
+      <c r="C254" s="7" t="inlineStr">
+        <is>
+          <t>No Python at all: the native core still works (no_python_core_use)</t>
+        </is>
+      </c>
+      <c r="D254" s="8" t="inlineStr">
+        <is>
+          <t>PART-AUTOMATED</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr"/>
+      <c r="F254" s="10" t="inlineStr"/>
+      <c r="G254" s="8" t="inlineStr"/>
+      <c r="H254" s="7" t="inlineStr">
+        <is>
+          <t>Log View, Petrophysics ▸ VSH ▾ ▸ VSH from Gamma Ray, Data ▸ Export LAS…, Plot ▸ Histogram, Data ▸ Curve Catalog (the Inspector pane) ▸ Equation Editor tab</t>
+        </is>
+      </c>
+      <c r="I254" s="7" t="inlineStr">
+        <is>
+          <t>the T-INS-02 machine with NO Python: `where python` and `where py` both find nothing, `SANDIBUMI_PYTHON` unset.</t>
+        </is>
+      </c>
+      <c r="J254" s="7" t="inlineStr">
+        <is>
+          <t>1. Open the T-INS-02 project; select SANDI-01; open a Log View; run Petrophysics ▸ VSH ▾ ▸ VSH from Gamma Ray; Data ▸ Export LAS…; open Plot ▸ Histogram of GR.
+2. Open Data ▸ Curve Catalog, switch to the Equation Editor tab and set Language to Python (numpy): the note under the language selector is where the engine says which interpreter it found.
+3. Try Data ▸ Import Logs ▾ ▸ Import DLIS… — pick any file and accept the set name — then, back in the Equation Editor, press Run on a one-line Python equation.
+   Expected: All four native operations in step 1 succeed. The language note carries a ⚠ saying no interpreter was found, by name. DLIS import shows its file dialog and set-name prompt as normal and refuses AFTER them but BEFORE any parsing — the `dlisio` preflight runs ahead of the parser subprocess (pinned by the ordering assertion in installation.rs) — naming `dlisio` and that no interpreter was found. The Equation Editor's Run is NOT refused up front: the run starts and fails with the engine's own message naming the missing interpreter. That is the residual `sb-ins.md` records for SB-INS-006 ("product-wide action gating is incomplete"); write the message in Notes, it is not a Fail. No crash, and no message tells you to install Python for a native feature.
+   Automated coverage - pinned, with a residual (Gate 3, 2026-09-02): `missing_python_does_not_block_project_open_native_computation_plotting_or_native_export` (installation.rs) drives the four native paths and the Python-only unavailable side in a test process. What stays yours: that the INSTALLED build on a machine with no interpreter behaves the same, and the wording of each refusal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B255" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-04</t>
+        </is>
+      </c>
+      <c r="C255" s="7" t="inlineStr">
+        <is>
+          <t>Every prerequisite surface tells the same truth</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="inlineStr"/>
+      <c r="F255" s="10" t="inlineStr"/>
+      <c r="G255" s="8" t="inlineStr"/>
+      <c r="H255" s="7" t="inlineStr">
+        <is>
+          <t>Project ▸ Help ▸ Prerequisites — the button opens the dialog titled *Capability prerequisites* (`installationSupportDialog.ts`) — `docs/INSTALLATION_PREREQUISITES.md`, README</t>
+        </is>
+      </c>
+      <c r="I255" s="7" t="inlineStr">
+        <is>
+          <t>the T-INS-03 machine (no Python); later the T-INS-05 machine (pack installed).</t>
+        </is>
+      </c>
+      <c r="J255" s="7" t="inlineStr">
+        <is>
+          <t>1. Open Project ▸ Help ▸ Prerequisites and read every row of the Capability prerequisites dialog.
+2. On the media open `docs/INSTALLATION_PREREQUISITES.md` and the README's prerequisites paragraph.
+3. Repeat step 1 on the pack machine after T-INS-05.
+   Expected: The dialog lists six capabilities — Python equations, DLIS import, Spreadsheet plate extraction, Workbook export, Document export, Deck export — each unavailable, each naming the package it needs. No surface says the product has no runtime dependency. On the pack machine the same rows read available with the interpreter path. Dialog and fragment agree row for row. Known gap (SB-INS-004): the manifest is six rows and other Python-backed actions exist — the image-conditioning Pillow path is one. Write down every Python-backed action you can find that the dialog does not name; that list is the evidence SB-INS-004 and SB-INS-026 are waiting for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-05</t>
+        </is>
+      </c>
+      <c r="C256" s="7" t="inlineStr">
+        <is>
+          <t>Offline install with the Python pack, network blocked (offline_install)</t>
+        </is>
+      </c>
+      <c r="D256" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E256" s="9" t="inlineStr"/>
+      <c r="F256" s="10" t="inlineStr"/>
+      <c r="G256" s="8" t="inlineStr"/>
+      <c r="H256" s="7" t="inlineStr">
+        <is>
+          <t>`msiexec`, the pack installer, a packet capture (`pktmon`), Project ▸ Help ▸ Prerequisites</t>
+        </is>
+      </c>
+      <c r="I256" s="7" t="inlineStr">
+        <is>
+          <t>the signed Python pack from increment G3-03 — if it does not exist yet, mark Blocked with the date and stop; a clean machine with every network adapter disabled or all outbound traffic blocked, and a capture running; MSI and pack on media.</t>
+        </is>
+      </c>
+      <c r="J256" s="7" t="inlineStr">
+        <is>
+          <t>1. Install the MSI per machine, then the pack, both silently.
+2. Sign in as the standard user; confirm the system environment variable `SANDIBUMI_PYTHON` points inside the pack.
+3. Open Project ▸ Help ▸ Prerequisites.
+4. Run one of each: a Python equation, a DLIS import, Workbook…, the report pane's Save Word…, and Deck….
+5. Stop the capture and look for any outbound request from `sandibumi.exe` or the pack's `python.exe`.
+   Expected: Every capability row reads available with the pack's interpreter; all five actions succeed; the capture holds zero outbound requests; nothing asks for the internet at any point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B257" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-06</t>
+        </is>
+      </c>
+      <c r="C257" s="7" t="inlineStr">
+        <is>
+          <t>A missing package is refused before work, by name, with the fix — then re-probed (missing_package)</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr"/>
+      <c r="F257" s="10" t="inlineStr"/>
+      <c r="G257" s="8" t="inlineStr"/>
+      <c r="H257" s="7" t="inlineStr">
+        <is>
+          <t>Equation Editor, Data ▸ Import Logs ▾ ▸ Import DLIS…, Plot ▸ Deliverables ▸ Workbook…, report pane Save Word…, Project ▸ Help ▸ Prerequisites</t>
+        </is>
+      </c>
+      <c r="I257" s="7" t="inlineStr">
+        <is>
+          <t>a machine with a Python 3.10+ that has numpy but NOT scipy, NOT dlisio, NOT xlsxwriter and NOT python-docx (`pip uninstall` them); `SANDIBUMI_PYTHON` pointing at it.</t>
+        </is>
+      </c>
+      <c r="J257" s="7" t="inlineStr">
+        <is>
+          <t>1. In the Equation Editor write an equation that calls `signal.savgol_filter(GR, 11, 2)` and run it.
+2. Data ▸ Import Logs ▾ ▸ Import DLIS….
+3. Plot ▸ Deliverables ▸ Workbook…; then render a report and press Save Word….
+4. Copy the pip command out of one of the messages, run it for python-docx, then open Project ▸ Help ▸ Prerequisites and look for a re-probe control inside the dialog; close and reopen it.
+   Expected: Step 1: the editor is available and the run fails AT the scipy name with a message that names the interpreter path and the pip command — never a bare `NameError`. Step 2: the file dialog and set-name prompt appear, then the import is refused before the file is parsed, naming `dlisio` and the interpreter. Step 3: Workbook… refuses BEFORE its save dialog, naming `xlsxwriter` and the interpreter; Save Word… does NOT — its save dialog opens first and the refusal naming `python-docx` arrives only after a path is picked. That is the gap `sb-ins.md` names for SB-INS-006 ("including the document-deliverable surface"); write it in Notes, it is not a Fail. Step 4: there is no re-probe control inside the dialog (Close is its only button) — that is SB-INS-007's open half, write "no re-probe control" in Notes; after closing and reopening, the Document export row reads available without a restart, because packages are probed on every open. Only the choice of INTERPRETER is fixed for the session: a Python installed on a machine that had none is seen after a restart, not before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B258" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-07</t>
+        </is>
+      </c>
+      <c r="C258" s="7" t="inlineStr">
+        <is>
+          <t>Interpreter precedence and the override (supported_external_python)</t>
+        </is>
+      </c>
+      <c r="D258" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E258" s="9" t="inlineStr"/>
+      <c r="F258" s="10" t="inlineStr"/>
+      <c r="G258" s="8" t="inlineStr"/>
+      <c r="H258" s="7" t="inlineStr">
+        <is>
+          <t>Data ▸ Curve Catalog ▸ Equation Editor tab (Language = Python), Project ▸ Help ▸ Prerequisites, the `SANDIBUMI_PYTHON` environment variable</t>
+        </is>
+      </c>
+      <c r="I258" s="7" t="inlineStr">
+        <is>
+          <t>two interpreters on one machine: A earlier in the discovery order (e.g. `%LOCALAPPDATA%\Programs\Python\Python313` WITHOUT numpy) and B later (Python312 WITH numpy); `SANDIBUMI_PYTHON` unset to start.</t>
+        </is>
+      </c>
+      <c r="J258" s="7" t="inlineStr">
+        <is>
+          <t>1. Launch; read the Equation Editor's language note (Language set to Python) and the Prerequisites dialog — its first line names the session Python and the rule that selected it, and every candidate follows as Selected or Rejected with a reason.
+2. Set `SANDIBUMI_PYTHON` (user environment) to B's `python.exe`; relaunch; read both again.
+3. Set it to a path that does not exist; relaunch.
+   Expected: Step 1: B is selected — A was found first and rejected for missing numpy — and the dialog names both candidates and the rejection reason. Step 2: every probe reports exactly B's path. Step 3: the app still launches; the override is the FIRST candidate and is listed Rejected with its path and reason — but it does not switch discovery off, it only goes first, so B is selected after it and the Python-backed rows read available with B's path. If the rows read unavailable, or the override's rejection is missing from the list, that is a Fail. No crash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B259" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-08</t>
+        </is>
+      </c>
+      <c r="C259" s="7" t="inlineStr">
+        <is>
+          <t>The installed settings template never changes; the user's copy does</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="inlineStr">
+        <is>
+          <t>PART-AUTOMATED</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr"/>
+      <c r="F259" s="10" t="inlineStr"/>
+      <c r="G259" s="8" t="inlineStr"/>
+      <c r="H259" s="7" t="inlineStr">
+        <is>
+          <t>Project ▸ Theme, Project ▸ Language, `%APPDATA%\com.sandibumi.petro\settings.json`</t>
+        </is>
+      </c>
+      <c r="I259" s="7" t="inlineStr">
+        <is>
+          <t>the T-INS-02 machine; a user account that has NEVER launched SandiBumi.</t>
+        </is>
+      </c>
+      <c r="J259" s="7" t="inlineStr">
+        <is>
+          <t>1. Find the settings template shipped inside the install directory recorded in T-INS-02 (search it for `settings*.json`; it is `resources/install/settings-template.json` in the bundle) and note its SHA-256.
+2. Launch as that user; switch the theme to Dark and the language to Bahasa Indonesia; close the app.
+3. Open `%APPDATA%\com.sandibumi.petro\settings.json` in a text editor; re-hash the installed template.
+4. Relaunch.
+   Expected: The installed template's hash is unchanged. The user copy exists, records the template version and digest it was made from, and carries both edits. The relaunch comes up Dark and in Bahasa Indonesia.
+   Automated coverage - pinned, with a residual (Gate 3, 2026-09-02): `first_run_materialises_a_user_copy_with_the_immutable_template_version_and_digest` (installation.rs) pins first-run creation, later-edit preservation, template byte identity and the version/digest provenance in a temp folder. What stays yours: the real paths on an installed machine, and that the app reads the copy back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-09</t>
+        </is>
+      </c>
+      <c r="C260" s="7" t="inlineStr">
+        <is>
+          <t>Upgrade in place keeps settings and both projects byte-identical (upgrade)</t>
+        </is>
+      </c>
+      <c r="D260" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr"/>
+      <c r="F260" s="10" t="inlineStr"/>
+      <c r="G260" s="8" t="inlineStr"/>
+      <c r="H260" s="7" t="inlineStr">
+        <is>
+          <t>`msiexec`, `certutil -hashfile`</t>
+        </is>
+      </c>
+      <c r="I260" s="7" t="inlineStr">
+        <is>
+          <t>the T-INS-08 machine with two project files (`uat-a.duckdb`, `uat-b.duckdb`, each opened once and the app closed) and the user settings; a NEWER candidate MSI — bump the version in `package.json`, `src-tauri/tauri.conf.json` AND `src-tauri/resources/install/settings-template.json` (`template_version`) on a throwaway branch, rebuild, and never commit the bump. The template version must equal the application version or the first launch under any FRESH profile refuses at setup (`materialize_user_settings` in installation.rs); an existing user copy is left alone, so a forgotten template bump would pass this test and only show on the next fresh account.</t>
+        </is>
+      </c>
+      <c r="J260" s="7" t="inlineStr">
+        <is>
+          <t>1. Hash both projects and `settings.json`.
+2. Install the newer MSI per machine over the old one.
+3. Launch as the user; open both projects; close.
+4. Re-hash all three.
+   Expected: The install succeeds with no prompt about user data. Both projects open. All three hashes are identical after the upgrade AND after being opened (a normal open writes nothing — T-SHIP-05). Apps shows the new version. Known gap (SB-INS-011, ABSENT): there is no migration report saying which settings were accepted, renamed, defaulted or rejected. If none appears, mark Blocked and write "no migration report (SB-INS-011)" — that mark is the evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B261" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-10</t>
+        </is>
+      </c>
+      <c r="C261" s="7" t="inlineStr">
+        <is>
+          <t>Rollback to the older candidate (rollback)</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr"/>
+      <c r="F261" s="10" t="inlineStr"/>
+      <c r="G261" s="8" t="inlineStr"/>
+      <c r="H261" s="7" t="inlineStr">
+        <is>
+          <t>Settings ▸ Apps, `msiexec`, `certutil -hashfile`</t>
+        </is>
+      </c>
+      <c r="I261" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-09 done.</t>
+        </is>
+      </c>
+      <c r="J261" s="7" t="inlineStr">
+        <is>
+          <t>1. Uninstall the newer version from Settings ▸ Apps with the default choices.
+2. Reinstall the older MSI per machine.
+3. Launch as the user; open both projects; re-hash.
+   Expected: The uninstall leaves `%APPDATA%\SandiBumi\`, `%APPDATA%\com.sandibumi.petro\` and both project files in place. The older build opens both projects and the hashes are unchanged. If the newer build had migrated the project schema, the older build must say so BY NAME rather than crash — write down exactly what it says.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-11</t>
+        </is>
+      </c>
+      <c r="C262" s="7" t="inlineStr">
+        <is>
+          <t>Uninstall with default choices leaves user data in place (uninstall_preservation)</t>
+        </is>
+      </c>
+      <c r="D262" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr"/>
+      <c r="F262" s="10" t="inlineStr"/>
+      <c r="G262" s="8" t="inlineStr"/>
+      <c r="H262" s="7" t="inlineStr">
+        <is>
+          <t>Settings ▸ Apps, Explorer</t>
+        </is>
+      </c>
+      <c r="I262" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-10 done.</t>
+        </is>
+      </c>
+      <c r="J262" s="7" t="inlineStr">
+        <is>
+          <t>1. Uninstall SandiBumi from Settings ▸ Apps with the default choices.
+2. Check the install directory, `%APPDATA%\SandiBumi\projects.json`, `trusted-code.json`, `%APPDATA%\com.sandibumi.petro\settings.json`, and both project files.
+   Expected: The install directory is gone. Every user file listed remains, byte-identical to its hash. No default step offered to delete user data. Whether a SEPARATE, explicit removal consent exists is SB-INS-022's design question — write down whether you saw one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B263" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-12</t>
+        </is>
+      </c>
+      <c r="C263" s="7" t="inlineStr">
+        <is>
+          <t>Recovery on the installed build: force-close while idle, then read the diagnostics</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr"/>
+      <c r="F263" s="10" t="inlineStr"/>
+      <c r="G263" s="8" t="inlineStr"/>
+      <c r="H263" s="7" t="inlineStr">
+        <is>
+          <t>Task Manager, the recovery offer at launch, Project ▸ Monitor ▸ Diagnostics…</t>
+        </is>
+      </c>
+      <c r="I263" s="7" t="inlineStr">
+        <is>
+          <t>a freshly reinstalled build (repeat T-INS-02); a project with a well; the app IDLE — nothing importing, running or exporting. This is the installed-build twin of T-SHELL-18 and T-PERF-08; the same rule applies: never kill during a write.</t>
+        </is>
+      </c>
+      <c r="J263" s="7" t="inlineStr">
+        <is>
+          <t>1. Arrange a distinctive workspace (two panes, a non-default well) and wait 30 s for autosave.
+2. Task Manager ▸ End task on SandiBumi.
+3. Relaunch.
+4. Project ▸ Monitor ▸ Diagnostics… and read the report in the pane.
+   Expected: The relaunch offers to recover the workspace and restores it on accept; the project opens. No `.corrupt-backup-*` file appears beside the project (an idle kill leaves a clean WAL) — if one does, recovery ran and the app still opened: note it. The report carries no crash record for this kill — an End task is not a panic; a real panic would have been written to `%APPDATA%\SandiBumi\crash-log.txt` and appear in the report, redacted and dated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-13</t>
+        </is>
+      </c>
+      <c r="C264" s="7" t="inlineStr">
+        <is>
+          <t>The support report from the installed build: complete, and redacted</t>
+        </is>
+      </c>
+      <c r="D264" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr"/>
+      <c r="F264" s="10" t="inlineStr"/>
+      <c r="G264" s="8" t="inlineStr"/>
+      <c r="H264" s="7" t="inlineStr">
+        <is>
+          <t>Project ▸ Help ▸ Prerequisites (the SB-INS-021 support payload, `installation_support`), Project ▸ Monitor ▸ Diagnostics… (`diagnostics.rs`, the sendable report)</t>
+        </is>
+      </c>
+      <c r="I264" s="7" t="inlineStr">
+        <is>
+          <t>any installed machine with a project holding wells and with whatever Python state that machine has.</t>
+        </is>
+      </c>
+      <c r="J264" s="7" t="inlineStr">
+        <is>
+          <t>1. Open Project ▸ Help ▸ Prerequisites and copy down by hand what it shows: the session Python and its rule, every candidate with its verdict and reason, each capability row with its package and version.
+2. Open Diagnostics…, press Build report, read the pane, press Save…, and open the saved text file.
+3. Search the file for every well name in the project and for the project's folder path.
+   Expected: Step 1 is the support report as adjudicated, and it is read off the screen because the dialog has no save or copy control — Close is its only button. Known gap (SB-INS-021, PARTIAL): it carries no application/build digest, no installer type, no OS architecture and no configuration-layer digests, and it cannot be exported — list which of these you found missing; that list is the evidence. Step 2: the file opens with the version line, names module ids, durations and counts, the OS and architecture, whether an interpreter was found (`found (numpy present)` / `not found`) and the scipy version — never the interpreter path, which carries a username and is left out on purpose, so there is no path to compare with step 1; compare found/not-found instead. Every well name appears as `WELL-1`, `WELL-2`… and the project path is masked; no curve values and no project samples anywhere; above the Save… button the pane says that parameter VALUES travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B265" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-14</t>
+        </is>
+      </c>
+      <c r="C265" s="7" t="inlineStr">
+        <is>
+          <t>The clean-machine matrix record, and the refusal that guards a release</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr"/>
+      <c r="F265" s="10" t="inlineStr"/>
+      <c r="G265" s="8" t="inlineStr"/>
+      <c r="H265" s="7" t="inlineStr">
+        <is>
+          <t>the results of T-INS-02 to T-INS-11; `installation.rs` (`CLEAN_MACHINE_SCENARIOS`)</t>
+        </is>
+      </c>
+      <c r="I265" s="7" t="inlineStr">
+        <is>
+          <t>the candidate's MSI digest, pack digest and commit (T-INS-01, T-INS-05); results for every (feature release × edition) you actually ran.</t>
+        </is>
+      </c>
+      <c r="J265" s="7" t="inlineStr">
+        <is>
+          <t>1. On the release date, capture Microsoft's list of serviced Windows 11 x64 feature releases; write the list and the date in Notes — it is captured then, never hard-coded.
+2. Fill one row per (feature release, edition, scenario) for the nine scenario ids — `standard_user`, `locked_down_user`, `offline_install`, `no_python_core_use`, `supported_external_python`, `missing_package`, `upgrade`, `rollback`, `uninstall_preservation` — with pass/fail and the three digests.
+3. Feed the record to the validator. The runner is increment G3-07; until it lands, run `cargo test one_failing_clean_machine_scenario_blocks_release_and_names_the_scenario` in the pinned shell to see the shape of the refusal.
+   Expected: A missing or failing cell is refused BY NAME — release, edition and scenario — and a complete green record is accepted and filed with the candidate. Until G3-07 exists there is no runner: mark Blocked and attach the filled table; the table is the evidence. (SB-CORE-042's "a machine enforces the gate on every change" is Jauhar's decision before this test can have a Pass.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>T-INS-15</t>
+        </is>
+      </c>
+      <c r="C266" s="7" t="inlineStr">
+        <is>
+          <t>The third-party inventory names the pack and fails on an unknown licence</t>
+        </is>
+      </c>
+      <c r="D266" s="8" t="inlineStr">
+        <is>
+          <t>YOURS</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr"/>
+      <c r="F266" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G266" s="8" t="inlineStr"/>
+      <c r="H266" s="7" t="inlineStr">
+        <is>
+          <t>`node tools/gen-third-party-licenses.mjs`, `THIRD-PARTY-LICENSES.md`</t>
+        </is>
+      </c>
+      <c r="I266" s="7" t="inlineStr">
+        <is>
+          <t>a repo checkout with `npm install` done; the pack's lock file if it exists.</t>
+        </is>
+      </c>
+      <c r="J266" s="7" t="inlineStr">
+        <is>
+          <t>1. Run `node tools/gen-third-party-licenses.mjs` (no flag): it rewrites the file and prints one line — `N crates, M npm packages, K copyleft, U undeclared`. Write the four numbers in Notes.
+2. Run it again with `--check` and read the exit code: it is 1 only when the file on disk is stale against a regeneration, 0 when current — a staleness gate, not a licence gate.
+3. Open `THIRD-PARTY-LICENSES.md`: read its preamble on Python packages; does it enumerate the Python pack's runtime and packages, and does it record a legal approval state?
+   Expected today (SB-INS-024, PRESENT-DIVERGENT): an `undeclared` count above 0 fails nothing — the generator counts unknown licences and carries on; the preamble states that Python packages are not distributed with SandiBumi, a statement the pack decision has made false; no pack inventory and no approval state exist. Write down the counts and exactly what the preamble says. After G3-07: an unknown licence makes it exit non-zero and names the package; the pack's runtime and packages are enumerated with versions and digests; legal approval is recorded separately as a human act, never inferred.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J251"/>
-  <conditionalFormatting sqref="D2:D251">
+  <autoFilter ref="A1:J266"/>
+  <conditionalFormatting sqref="D2:D266">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"YOURS"</formula>
     </cfRule>
@@ -13006,7 +13675,7 @@
       <formula>"GATE-PINNED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E251">
+  <conditionalFormatting sqref="E2:E266">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
       <formula>"Pass"</formula>
     </cfRule>
@@ -13018,7 +13687,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E251" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid result" error="Pick Pass, Fail or Blocked from the dropdown, or leave the cell blank." type="list" errorStyle="stop">
+    <dataValidation sqref="E2:E266" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid result" error="Pick Pass, Fail or Blocked from the dropdown, or leave the cell blank." type="list" errorStyle="stop">
       <formula1>"Pass,Fail,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13032,7 +13701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13111,27 +13780,27 @@
         </is>
       </c>
       <c r="C2" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A2)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A2)</f>
         <v/>
       </c>
       <c r="D2" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A2,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A2,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A2,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A2,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F2" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A2,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A2,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G2" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A2,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A2,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H2" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A2,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A2,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I2" s="3">
@@ -13155,27 +13824,27 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A3)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A3)</f>
         <v/>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A3,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A3,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A3,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A3,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A3,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A3,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G3" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A3,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A3,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H3" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A3,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A3,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I3" s="3">
@@ -13199,27 +13868,27 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A4)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A4)</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A4,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A4,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A4,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A4,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A4,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A4,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A4,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A4,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H4" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A4,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A4,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I4" s="3">
@@ -13243,27 +13912,27 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A5)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A5)</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A5,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A5,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A5,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A5,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A5,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A5,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A5,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A5,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A5,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A5,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I5" s="3">
@@ -13287,27 +13956,27 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A6)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A6)</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A6,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A6,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A6,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A6,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A6,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A6,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A6,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A6,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A6,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A6,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I6" s="3">
@@ -13331,27 +14000,27 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A7)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A7)</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A7,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A7,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A7,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A7,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A7,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A7,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A7,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A7,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A7,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A7,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I7" s="3">
@@ -13375,27 +14044,27 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A8)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A8)</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A8,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A8,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A8,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A8,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A8,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A8,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A8,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A8,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H8" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A8,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A8,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I8" s="3">
@@ -13419,27 +14088,27 @@
         </is>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A9)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A9)</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A9,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A9,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A9,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A9,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A9,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A9,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A9,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A9,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H9" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A9,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A9,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I9" s="3">
@@ -13463,27 +14132,27 @@
         </is>
       </c>
       <c r="C10" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A10)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A10)</f>
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A10,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A10,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A10,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A10,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A10,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A10,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G10" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A10,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A10,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H10" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A10,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A10,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I10" s="3">
@@ -13507,27 +14176,27 @@
         </is>
       </c>
       <c r="C11" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A11)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A11)</f>
         <v/>
       </c>
       <c r="D11" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A11,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A11,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E11" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A11,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A11,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F11" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A11,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A11,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G11" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A11,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A11,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H11" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A11,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A11,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I11" s="3">
@@ -13551,27 +14220,27 @@
         </is>
       </c>
       <c r="C12" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A12)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A12)</f>
         <v/>
       </c>
       <c r="D12" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A12,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A12,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E12" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A12,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A12,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F12" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A12,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A12,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G12" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A12,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A12,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H12" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A12,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A12,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I12" s="3">
@@ -13595,27 +14264,27 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A13)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A13)</f>
         <v/>
       </c>
       <c r="D13" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A13,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A13,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E13" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A13,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A13,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F13" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A13,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A13,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G13" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A13,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A13,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H13" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A13,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A13,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I13" s="3">
@@ -13639,27 +14308,27 @@
         </is>
       </c>
       <c r="C14" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A14)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A14)</f>
         <v/>
       </c>
       <c r="D14" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A14,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A14,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E14" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A14,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A14,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F14" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A14,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A14,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G14" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A14,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A14,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H14" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A14,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A14,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I14" s="3">
@@ -13683,27 +14352,27 @@
         </is>
       </c>
       <c r="C15" s="3">
-        <f>COUNTIF(Tests!$A$2:$A$251,$A15)</f>
+        <f>COUNTIF(Tests!$A$2:$A$266,$A15)</f>
         <v/>
       </c>
       <c r="D15" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A15,Tests!$D$2:$D$251,"YOURS")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A15,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
       <c r="E15" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A15,Tests!$D$2:$D$251,"YOURS",Tests!$E$2:$E$251,"")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A15,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
       <c r="F15" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A15,Tests!$E$2:$E$251,"Pass")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A15,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
       <c r="G15" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A15,Tests!$E$2:$E$251,"Fail")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A15,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
       <c r="H15" s="3">
-        <f>COUNTIFS(Tests!$A$2:$A$251,$A15,Tests!$E$2:$E$251,"Blocked")</f>
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A15,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
       <c r="I15" s="3">
@@ -13716,57 +14385,101 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C16" s="4">
-        <f>SUM(C2:C15)</f>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Installation, offline runtime &amp; recovery (Gate 3)</t>
+        </is>
+      </c>
+      <c r="C16" s="3">
+        <f>COUNTIF(Tests!$A$2:$A$266,$A16)</f>
         <v/>
       </c>
-      <c r="D16" s="4">
-        <f>SUM(D2:D15)</f>
+      <c r="D16" s="3">
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A16,Tests!$D$2:$D$266,"YOURS")</f>
         <v/>
       </c>
-      <c r="E16" s="4">
-        <f>SUM(E2:E15)</f>
+      <c r="E16" s="3">
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A16,Tests!$D$2:$D$266,"YOURS",Tests!$E$2:$E$266,"")</f>
         <v/>
       </c>
-      <c r="F16" s="4">
-        <f>SUM(F2:F15)</f>
+      <c r="F16" s="3">
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A16,Tests!$E$2:$E$266,"Pass")</f>
         <v/>
       </c>
-      <c r="G16" s="4">
-        <f>SUM(G2:G15)</f>
+      <c r="G16" s="3">
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A16,Tests!$E$2:$E$266,"Fail")</f>
         <v/>
       </c>
-      <c r="H16" s="4">
-        <f>SUM(H2:H15)</f>
+      <c r="H16" s="3">
+        <f>COUNTIFS(Tests!$A$2:$A$266,$A16,Tests!$E$2:$E$266,"Blocked")</f>
         <v/>
       </c>
-      <c r="I16" s="4">
-        <f>SUM(I2:I15)</f>
+      <c r="I16" s="3">
+        <f>C16-F16-G16-H16</f>
         <v/>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <f>IFERROR((F16+G16+H16)/C16,0)</f>
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C17" s="4">
+        <f>SUM(C2:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="4">
+        <f>SUM(D2:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="4">
+        <f>SUM(E2:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4">
+        <f>SUM(F2:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>SUM(G2:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>SUM(H2:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>SUM(I2:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>IFERROR((F17+G17+H17)/C17,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
